--- a/InputData/ccs/CCSTaSCaS/CCS Transportation and Storage Costs and Subsidies.xlsx
+++ b/InputData/ccs/CCSTaSCaS/CCS Transportation and Storage Costs and Subsidies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\ccs\CCSTaSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\ccs\CCSTaSCaS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1762EE-E61A-4841-8A89-DF6D42FF5594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F80A145-E2CC-4AB2-AF81-FB583B4B6E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32880" yWindow="1710" windowWidth="21360" windowHeight="14610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Source:</t>
   </si>
@@ -59,13 +61,16 @@
     <t>Value from study (2021 $)</t>
   </si>
   <si>
-    <t>2018 to 2012 $</t>
-  </si>
-  <si>
     <t>Transportation and Storage Subsidies ($ per metric ton CO2)</t>
   </si>
   <si>
     <t>CCSTaSCaS CCS Transportation and Storage Costs and Subsidies</t>
+  </si>
+  <si>
+    <t>2021 to 2012 $</t>
+  </si>
+  <si>
+    <t>2026-10-23: the factor above was a 2018-to-2012 factor (0.9143) applied to a 2021$ value. Now CPI-U annual average 2012/2021 (229.594/270.970), the same CPI-U series as the 2018 (229.594/251.107) and 2022 (229.594/292.655) factors used in other EPS workbooks.</t>
   </si>
 </sst>
 </file>
@@ -446,19 +451,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.26953125" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,35 +471,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -502,12 +507,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9143273584567535</v>
+        <f>229.594/270.97</f>
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -525,13 +536,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.1796875" customWidth="1"/>
-    <col min="2" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.140625" customWidth="1"/>
+    <col min="2" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -623,132 +634,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="C2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="D2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="E2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="F2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="G2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="H2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="I2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="J2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="K2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="L2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="M2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="N2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="O2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="P2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="Q2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="R2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="S2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="T2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="U2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="V2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="W2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="X2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="Y2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="Z2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="AA2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="AB2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="AC2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="AD2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>19.487994980994202</v>
       </c>
       <c r="AE2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+        <v>19.487994980994202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="K4" s="2"/>
     </row>
   </sheetData>
@@ -762,13 +773,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.1796875" customWidth="1"/>
-    <col min="2" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.140625" customWidth="1"/>
+    <col min="2" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -860,9 +871,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -955,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="K4" s="2"/>
     </row>
   </sheetData>
